--- a/docs/verification/files/rocscience/vp077b.xlsx
+++ b/docs/verification/files/rocscience/vp077b.xlsx
@@ -6728,7 +6728,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>2861300.0</v>
       </c>
@@ -6854,7 +6856,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>355100.0</v>
       </c>

--- a/docs/verification/files/rocscience/vp077b.xlsx
+++ b/docs/verification/files/rocscience/vp077b.xlsx
@@ -6732,10 +6732,10 @@
         <v>0.0</v>
       </c>
       <c r="M11" s="3">
-        <v>2861300.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -6860,10 +6860,10 @@
         <v>0.0</v>
       </c>
       <c r="M12" s="3">
-        <v>355100.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="N12" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
